--- a/References/TercihAnalizi Database Tables/programs.xlsx
+++ b/References/TercihAnalizi Database Tables/programs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4969" uniqueCount="4969">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5225" uniqueCount="5225">
   <si>
     <t>id</t>
   </si>
@@ -13305,7 +13305,7 @@
     <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
   </si>
   <si>
-    <t>["Sa\u00e7 Bak\u0131m\u0131 ve G\u00fczellik Hizmetleri"]</t>
+    <t>["Saç Bakımı ve Güzellik Hizmetleri", "Saç ve Güzellik Uygulamaları"]</t>
   </si>
   <si>
     <t>yok</t>
@@ -13329,7 +13329,7 @@
     <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
   </si>
   <si>
-    <t>["Sa\u011fl\u0131k Bilgi Sistemleri Teknikerli\u011fi"]</t>
+    <t>["Sağlık Bilgi Sistemleri Teknikerliği", "Dijital Sağlık Sistemleri Teknikerliği"]</t>
   </si>
   <si>
     <t>yok</t>
@@ -14920,6 +14920,774 @@
   </si>
   <si>
     <t>19052</t>
+  </si>
+  <si>
+    <t>732</t>
+  </si>
+  <si>
+    <t>Akıllı Altyapılar Teknikerliği</t>
+  </si>
+  <si>
+    <t>RCI</t>
+  </si>
+  <si>
+    <t>HFW</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Akıllı Altyapılar Teknikerliği"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998878</t>
+  </si>
+  <si>
+    <t>811</t>
+  </si>
+  <si>
+    <t>Akıllı Sera Teknolojileri</t>
+  </si>
+  <si>
+    <t>RCI</t>
+  </si>
+  <si>
+    <t>HPV</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Akıllı Sera Teknolojileri"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998879</t>
+  </si>
+  <si>
+    <t>811</t>
+  </si>
+  <si>
+    <t>Akıllı Tarım ve Gıda Yönetimi</t>
+  </si>
+  <si>
+    <t>ERS</t>
+  </si>
+  <si>
+    <t>FVW</t>
+  </si>
+  <si>
+    <t>{"osym_table": "4", "osym_score_type": "EA"}</t>
+  </si>
+  <si>
+    <t>["Akıllı Tarım ve Gıda Yönetimi"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998880</t>
+  </si>
+  <si>
+    <t>811</t>
+  </si>
+  <si>
+    <t>Dijital Tarım Teknolojileri</t>
+  </si>
+  <si>
+    <t>RCI</t>
+  </si>
+  <si>
+    <t>HFV</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Dijital Tarım Teknolojileri"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998881</t>
+  </si>
+  <si>
+    <t>522</t>
+  </si>
+  <si>
+    <t>Doğa Koruma ve Biyoçeşitlilik Yönetimi</t>
+  </si>
+  <si>
+    <t>ERC</t>
+  </si>
+  <si>
+    <t>FVW</t>
+  </si>
+  <si>
+    <t>{"osym_table": "4", "osym_score_type": "SAY"}</t>
+  </si>
+  <si>
+    <t>["Doğa Koruma ve Biyoçeşitlilik Yönetimi"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998882</t>
+  </si>
+  <si>
+    <t>713</t>
+  </si>
+  <si>
+    <t>Elektrik Makineleri Bakım ve Onarımı</t>
+  </si>
+  <si>
+    <t>RIC</t>
+  </si>
+  <si>
+    <t>HFW</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Elektrik Makineleri Bakım ve Onarımı"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998883</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>Eğitim Bilimleri</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>PVF</t>
+  </si>
+  <si>
+    <t>{"osym_table": "4", "osym_score_type": "EA"}</t>
+  </si>
+  <si>
+    <t>["Eğitim Bilimleri"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998884</t>
+  </si>
+  <si>
+    <t>716</t>
+  </si>
+  <si>
+    <t>Fiber Tekne İmalatı ve Kompozit Kalıp Teknolojileri</t>
+  </si>
+  <si>
+    <t>RCI</t>
+  </si>
+  <si>
+    <t>FHP</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Fiber Tekne İmalatı ve Kompozit Kalıp Teknolojileri"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998885</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>Filoloji</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>FPV</t>
+  </si>
+  <si>
+    <t>{"osym_table": "4", "osym_score_type": "DİL"}</t>
+  </si>
+  <si>
+    <t>["Filoloji"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998886</t>
+  </si>
+  <si>
+    <t>715</t>
+  </si>
+  <si>
+    <t>Hassas Tarım ve Tarımsal Robotlar</t>
+  </si>
+  <si>
+    <t>RCI</t>
+  </si>
+  <si>
+    <t>HFV</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Hassas Tarım ve Tarımsal Robotlar"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998887</t>
+  </si>
+  <si>
+    <t>714</t>
+  </si>
+  <si>
+    <t>Havacılık Elektroniği Teknolojileri</t>
+  </si>
+  <si>
+    <t>RIC</t>
+  </si>
+  <si>
+    <t>HFP</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Havacılık Elektroniği Teknolojileri"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998888</t>
+  </si>
+  <si>
+    <t>713</t>
+  </si>
+  <si>
+    <t>Hidrojen ve Enerji Depolama Teknikerliği</t>
+  </si>
+  <si>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>WVF</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Hidrojen ve Enerji Depolama Teknikerliği"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998889</t>
+  </si>
+  <si>
+    <t>715</t>
+  </si>
+  <si>
+    <t>Hidrolik ve Pnömatik Teknikerliği</t>
+  </si>
+  <si>
+    <t>RIC</t>
+  </si>
+  <si>
+    <t>HPF</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Hidrolik ve Pnömatik Teknikerliği"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998890</t>
+  </si>
+  <si>
+    <t>1041</t>
+  </si>
+  <si>
+    <t>Karayolu Yük Taşıtı Sürücülüğü</t>
+  </si>
+  <si>
+    <t>RC</t>
+  </si>
+  <si>
+    <t>HFW</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Karayolu Yük Taşıtı Sürücülüğü"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998891</t>
+  </si>
+  <si>
+    <t>522</t>
+  </si>
+  <si>
+    <t>Karbon Yönetimi Teknikerliği</t>
+  </si>
+  <si>
+    <t>RCE</t>
+  </si>
+  <si>
+    <t>VWH</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Karbon Yönetimi Teknikerliği"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998892</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>Ofis Teknolojileri ve Veri Yönetimi</t>
+  </si>
+  <si>
+    <t>CER</t>
+  </si>
+  <si>
+    <t>PHW</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Ofis Teknolojileri ve Veri Yönetimi"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998893</t>
+  </si>
+  <si>
+    <t>714</t>
+  </si>
+  <si>
+    <t>Optoelektronik ve Elektro Optik Teknolojileri</t>
+  </si>
+  <si>
+    <t>RIC</t>
+  </si>
+  <si>
+    <t>HWF</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Optoelektronik ve Elektro Optik Teknolojileri"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998894</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>Sırp Dili ve Edebiyatı</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>FPV</t>
+  </si>
+  <si>
+    <t>{"osym_table": "4", "osym_score_type": "DİL"}</t>
+  </si>
+  <si>
+    <t>["Sırp Dili ve Edebiyatı"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998895</t>
+  </si>
+  <si>
+    <t>715</t>
+  </si>
+  <si>
+    <t>Talaşlı Üretim Teknikerliği</t>
+  </si>
+  <si>
+    <t>RC</t>
+  </si>
+  <si>
+    <t>HPF</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Talaşlı Üretim Teknikerliği"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998896</t>
+  </si>
+  <si>
+    <t>715</t>
+  </si>
+  <si>
+    <t>Tarım Makineleri ve Teknolojileri</t>
+  </si>
+  <si>
+    <t>RC</t>
+  </si>
+  <si>
+    <t>PHW</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Tarım Makineleri ve Teknolojileri"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998897</t>
+  </si>
+  <si>
+    <t>914</t>
+  </si>
+  <si>
+    <t>Tele-Sağlık Teknikerliği</t>
+  </si>
+  <si>
+    <t>IRC</t>
+  </si>
+  <si>
+    <t>VFH</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Tele-Sağlık Teknikerliği"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998898</t>
+  </si>
+  <si>
+    <t>1015</t>
+  </si>
+  <si>
+    <t>Turizm ve Gastronomi Yönetimi Programları</t>
+  </si>
+  <si>
+    <t>ECS</t>
+  </si>
+  <si>
+    <t>FPW</t>
+  </si>
+  <si>
+    <t>{"osym_table": "4", "osym_score_type": "EA"}</t>
+  </si>
+  <si>
+    <t>["Turizm ve Gastronomi Yönetimi Programları"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998899</t>
+  </si>
+  <si>
+    <t>914</t>
+  </si>
+  <si>
+    <t>Tıbbi Veri İşleme Teknikerliği</t>
+  </si>
+  <si>
+    <t>IRC</t>
+  </si>
+  <si>
+    <t>VFH</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Tıbbi Veri İşleme Teknikerliği"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998900</t>
+  </si>
+  <si>
+    <t>532</t>
+  </si>
+  <si>
+    <t>Uzaktan Algılama ve Coğrafi Bilgi Sistemleri</t>
+  </si>
+  <si>
+    <t>IRC</t>
+  </si>
+  <si>
+    <t>VFW</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Uzaktan Algılama ve Coğrafi Bilgi Sistemleri"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998901</t>
+  </si>
+  <si>
+    <t>732</t>
+  </si>
+  <si>
+    <t>Yapı Yüzeyi Tasarım Teknikerliği</t>
+  </si>
+  <si>
+    <t>RCI</t>
+  </si>
+  <si>
+    <t>HPF</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Yapı Yüzeyi Tasarım Teknikerliği"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998902</t>
+  </si>
+  <si>
+    <t>713</t>
+  </si>
+  <si>
+    <t>Yenilenebilir Enerji Teknikerliği</t>
+  </si>
+  <si>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>WVF</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Yenilenebilir Enerji Teknikerliği"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998903</t>
+  </si>
+  <si>
+    <t>732</t>
+  </si>
+  <si>
+    <t>Yeşil ve Ekolojik Bina Teknikerliği</t>
+  </si>
+  <si>
+    <t>RCI</t>
+  </si>
+  <si>
+    <t>HPF</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Yeşil ve Ekolojik Bina Teknikerliği"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998904</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>Çerkez Dili ve Edebiyatı</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>FPV</t>
+  </si>
+  <si>
+    <t>{"osym_table": "4", "osym_score_type": "DİL"}</t>
+  </si>
+  <si>
+    <t>["Çerkez Dili ve Edebiyatı"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998905</t>
+  </si>
+  <si>
+    <t>712</t>
+  </si>
+  <si>
+    <t>Çevre Sağlığı ve Çevresel Risk Yönetimi Teknikerliği</t>
+  </si>
+  <si>
+    <t>SIE</t>
+  </si>
+  <si>
+    <t>VWH</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Çevre Sağlığı ve Çevresel Risk Yönetimi Teknikerliği"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998906</t>
+  </si>
+  <si>
+    <t>712</t>
+  </si>
+  <si>
+    <t>Çevresel Ölçüm ve İzleme Sistemleri Teknikerliği</t>
+  </si>
+  <si>
+    <t>IRC</t>
+  </si>
+  <si>
+    <t>VWO</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Çevresel Ölçüm ve İzleme Sistemleri Teknikerliği"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998907</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>İspanyolca Mütercim ve Tercümanlık</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>PWO</t>
+  </si>
+  <si>
+    <t>{"osym_table": "4", "osym_score_type": "DİL"}</t>
+  </si>
+  <si>
+    <t>["İspanyolca Mütercim ve Tercümanlık"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998908</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>Su ve Atık Yönetimi Teknikerliği</t>
+  </si>
+  <si>
+    <t>RC</t>
+  </si>
+  <si>
+    <t>VOF</t>
+  </si>
+  <si>
+    <t>{"osym_table": "3", "osym_score_type": "TYT"}</t>
+  </si>
+  <si>
+    <t>["Su ve Atık Yönetimi Teknikerliği"]</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>998909</t>
   </si>
 </sst>
 </file>
@@ -14970,7 +15738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q620"/>
+  <dimension ref="A1:Q652"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44279,7 +45047,7 @@
         <v>45726.668749999997</v>
       </c>
       <c r="Q553" s="2">
-        <v>45726.739768518521</v>
+        <v>46108.5</v>
       </c>
     </row>
     <row r="554">
@@ -44332,7 +45100,7 @@
         <v>45726.668749999997</v>
       </c>
       <c r="Q554" s="2">
-        <v>45726.739768518521</v>
+        <v>46108.5</v>
       </c>
     </row>
     <row r="555">
@@ -47833,6 +48601,1702 @@
         <v>45726.757094907407</v>
       </c>
     </row>
+    <row r="621">
+      <c r="A621">
+        <v>622</v>
+      </c>
+      <c r="B621" t="s">
+        <v>4969</v>
+      </c>
+      <c r="C621">
+        <v>220</v>
+      </c>
+      <c r="D621">
+        <v>325</v>
+      </c>
+      <c r="E621" t="s">
+        <v>4970</v>
+      </c>
+      <c r="F621">
+        <v>1</v>
+      </c>
+      <c r="G621">
+        <v>7</v>
+      </c>
+      <c r="H621" t="s">
+        <v>4971</v>
+      </c>
+      <c r="I621" t="s">
+        <v>4972</v>
+      </c>
+      <c r="J621">
+        <v>10</v>
+      </c>
+      <c r="K621">
+        <v>2</v>
+      </c>
+      <c r="L621" t="s">
+        <v>4973</v>
+      </c>
+      <c r="M621" t="s">
+        <v>4974</v>
+      </c>
+      <c r="N621" t="s">
+        <v>4975</v>
+      </c>
+      <c r="O621" t="s">
+        <v>4976</v>
+      </c>
+      <c r="P621" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q621" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622">
+        <v>623</v>
+      </c>
+      <c r="B622" t="s">
+        <v>4977</v>
+      </c>
+      <c r="C622">
+        <v>220</v>
+      </c>
+      <c r="D622">
+        <v>326</v>
+      </c>
+      <c r="E622" t="s">
+        <v>4978</v>
+      </c>
+      <c r="F622">
+        <v>1</v>
+      </c>
+      <c r="G622">
+        <v>6</v>
+      </c>
+      <c r="H622" t="s">
+        <v>4979</v>
+      </c>
+      <c r="I622" t="s">
+        <v>4980</v>
+      </c>
+      <c r="J622">
+        <v>10</v>
+      </c>
+      <c r="K622">
+        <v>2</v>
+      </c>
+      <c r="L622" t="s">
+        <v>4981</v>
+      </c>
+      <c r="M622" t="s">
+        <v>4982</v>
+      </c>
+      <c r="N622" t="s">
+        <v>4983</v>
+      </c>
+      <c r="O622" t="s">
+        <v>4984</v>
+      </c>
+      <c r="P622" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q622" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623">
+        <v>624</v>
+      </c>
+      <c r="B623" t="s">
+        <v>4985</v>
+      </c>
+      <c r="C623">
+        <v>220</v>
+      </c>
+      <c r="D623">
+        <v>279</v>
+      </c>
+      <c r="E623" t="s">
+        <v>4986</v>
+      </c>
+      <c r="F623">
+        <v>1</v>
+      </c>
+      <c r="G623">
+        <v>6</v>
+      </c>
+      <c r="H623" t="s">
+        <v>4987</v>
+      </c>
+      <c r="I623" t="s">
+        <v>4988</v>
+      </c>
+      <c r="J623">
+        <v>50</v>
+      </c>
+      <c r="K623">
+        <v>4</v>
+      </c>
+      <c r="L623" t="s">
+        <v>4989</v>
+      </c>
+      <c r="M623" t="s">
+        <v>4990</v>
+      </c>
+      <c r="N623" t="s">
+        <v>4991</v>
+      </c>
+      <c r="O623" t="s">
+        <v>4992</v>
+      </c>
+      <c r="P623" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q623" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624">
+        <v>625</v>
+      </c>
+      <c r="B624" t="s">
+        <v>4993</v>
+      </c>
+      <c r="C624">
+        <v>220</v>
+      </c>
+      <c r="D624">
+        <v>327</v>
+      </c>
+      <c r="E624" t="s">
+        <v>4994</v>
+      </c>
+      <c r="F624">
+        <v>1</v>
+      </c>
+      <c r="G624">
+        <v>6</v>
+      </c>
+      <c r="H624" t="s">
+        <v>4995</v>
+      </c>
+      <c r="I624" t="s">
+        <v>4996</v>
+      </c>
+      <c r="J624">
+        <v>10</v>
+      </c>
+      <c r="K624">
+        <v>2</v>
+      </c>
+      <c r="L624" t="s">
+        <v>4997</v>
+      </c>
+      <c r="M624" t="s">
+        <v>4998</v>
+      </c>
+      <c r="N624" t="s">
+        <v>4999</v>
+      </c>
+      <c r="O624" t="s">
+        <v>5000</v>
+      </c>
+      <c r="P624" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q624" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625">
+        <v>626</v>
+      </c>
+      <c r="B625" t="s">
+        <v>5001</v>
+      </c>
+      <c r="C625">
+        <v>220</v>
+      </c>
+      <c r="D625">
+        <v>303</v>
+      </c>
+      <c r="E625" t="s">
+        <v>5002</v>
+      </c>
+      <c r="F625">
+        <v>1</v>
+      </c>
+      <c r="G625">
+        <v>3</v>
+      </c>
+      <c r="H625" t="s">
+        <v>5003</v>
+      </c>
+      <c r="I625" t="s">
+        <v>5004</v>
+      </c>
+      <c r="J625">
+        <v>60</v>
+      </c>
+      <c r="K625">
+        <v>4</v>
+      </c>
+      <c r="L625" t="s">
+        <v>5005</v>
+      </c>
+      <c r="M625" t="s">
+        <v>5006</v>
+      </c>
+      <c r="N625" t="s">
+        <v>5007</v>
+      </c>
+      <c r="O625" t="s">
+        <v>5008</v>
+      </c>
+      <c r="P625" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q625" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626">
+        <v>627</v>
+      </c>
+      <c r="B626" t="s">
+        <v>5009</v>
+      </c>
+      <c r="C626">
+        <v>220</v>
+      </c>
+      <c r="D626">
+        <v>80</v>
+      </c>
+      <c r="E626" t="s">
+        <v>5010</v>
+      </c>
+      <c r="F626">
+        <v>1</v>
+      </c>
+      <c r="G626">
+        <v>7</v>
+      </c>
+      <c r="H626" t="s">
+        <v>5011</v>
+      </c>
+      <c r="I626" t="s">
+        <v>5012</v>
+      </c>
+      <c r="J626">
+        <v>10</v>
+      </c>
+      <c r="K626">
+        <v>2</v>
+      </c>
+      <c r="L626" t="s">
+        <v>5013</v>
+      </c>
+      <c r="M626" t="s">
+        <v>5014</v>
+      </c>
+      <c r="N626" t="s">
+        <v>5015</v>
+      </c>
+      <c r="O626" t="s">
+        <v>5016</v>
+      </c>
+      <c r="P626" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q626" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627">
+        <v>628</v>
+      </c>
+      <c r="B627" t="s">
+        <v>5017</v>
+      </c>
+      <c r="C627">
+        <v>220</v>
+      </c>
+      <c r="D627">
+        <v>328</v>
+      </c>
+      <c r="E627" t="s">
+        <v>5018</v>
+      </c>
+      <c r="F627">
+        <v>1</v>
+      </c>
+      <c r="G627">
+        <v>12</v>
+      </c>
+      <c r="H627" t="s">
+        <v>5019</v>
+      </c>
+      <c r="I627" t="s">
+        <v>5020</v>
+      </c>
+      <c r="J627">
+        <v>70</v>
+      </c>
+      <c r="K627">
+        <v>4</v>
+      </c>
+      <c r="L627" t="s">
+        <v>5021</v>
+      </c>
+      <c r="M627" t="s">
+        <v>5022</v>
+      </c>
+      <c r="N627" t="s">
+        <v>5023</v>
+      </c>
+      <c r="O627" t="s">
+        <v>5024</v>
+      </c>
+      <c r="P627" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q627" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628">
+        <v>629</v>
+      </c>
+      <c r="B628" t="s">
+        <v>5025</v>
+      </c>
+      <c r="C628">
+        <v>220</v>
+      </c>
+      <c r="D628">
+        <v>119</v>
+      </c>
+      <c r="E628" t="s">
+        <v>5026</v>
+      </c>
+      <c r="F628">
+        <v>1</v>
+      </c>
+      <c r="G628">
+        <v>5</v>
+      </c>
+      <c r="H628" t="s">
+        <v>5027</v>
+      </c>
+      <c r="I628" t="s">
+        <v>5028</v>
+      </c>
+      <c r="J628">
+        <v>10</v>
+      </c>
+      <c r="K628">
+        <v>2</v>
+      </c>
+      <c r="L628" t="s">
+        <v>5029</v>
+      </c>
+      <c r="M628" t="s">
+        <v>5030</v>
+      </c>
+      <c r="N628" t="s">
+        <v>5031</v>
+      </c>
+      <c r="O628" t="s">
+        <v>5032</v>
+      </c>
+      <c r="P628" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q628" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629">
+        <v>630</v>
+      </c>
+      <c r="B629" t="s">
+        <v>5033</v>
+      </c>
+      <c r="C629">
+        <v>220</v>
+      </c>
+      <c r="D629">
+        <v>8</v>
+      </c>
+      <c r="E629" t="s">
+        <v>5034</v>
+      </c>
+      <c r="F629">
+        <v>1</v>
+      </c>
+      <c r="G629">
+        <v>11</v>
+      </c>
+      <c r="H629" t="s">
+        <v>5035</v>
+      </c>
+      <c r="I629" t="s">
+        <v>5036</v>
+      </c>
+      <c r="J629">
+        <v>90</v>
+      </c>
+      <c r="K629">
+        <v>4</v>
+      </c>
+      <c r="L629" t="s">
+        <v>5037</v>
+      </c>
+      <c r="M629" t="s">
+        <v>5038</v>
+      </c>
+      <c r="N629" t="s">
+        <v>5039</v>
+      </c>
+      <c r="O629" t="s">
+        <v>5040</v>
+      </c>
+      <c r="P629" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q629" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630">
+        <v>631</v>
+      </c>
+      <c r="B630" t="s">
+        <v>5041</v>
+      </c>
+      <c r="C630">
+        <v>220</v>
+      </c>
+      <c r="D630">
+        <v>329</v>
+      </c>
+      <c r="E630" t="s">
+        <v>5042</v>
+      </c>
+      <c r="F630">
+        <v>1</v>
+      </c>
+      <c r="G630">
+        <v>6</v>
+      </c>
+      <c r="H630" t="s">
+        <v>5043</v>
+      </c>
+      <c r="I630" t="s">
+        <v>5044</v>
+      </c>
+      <c r="J630">
+        <v>10</v>
+      </c>
+      <c r="K630">
+        <v>2</v>
+      </c>
+      <c r="L630" t="s">
+        <v>5045</v>
+      </c>
+      <c r="M630" t="s">
+        <v>5046</v>
+      </c>
+      <c r="N630" t="s">
+        <v>5047</v>
+      </c>
+      <c r="O630" t="s">
+        <v>5048</v>
+      </c>
+      <c r="P630" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q630" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631">
+        <v>632</v>
+      </c>
+      <c r="B631" t="s">
+        <v>5049</v>
+      </c>
+      <c r="C631">
+        <v>220</v>
+      </c>
+      <c r="D631">
+        <v>291</v>
+      </c>
+      <c r="E631" t="s">
+        <v>5050</v>
+      </c>
+      <c r="F631">
+        <v>1</v>
+      </c>
+      <c r="G631">
+        <v>7</v>
+      </c>
+      <c r="H631" t="s">
+        <v>5051</v>
+      </c>
+      <c r="I631" t="s">
+        <v>5052</v>
+      </c>
+      <c r="J631">
+        <v>10</v>
+      </c>
+      <c r="K631">
+        <v>2</v>
+      </c>
+      <c r="L631" t="s">
+        <v>5053</v>
+      </c>
+      <c r="M631" t="s">
+        <v>5054</v>
+      </c>
+      <c r="N631" t="s">
+        <v>5055</v>
+      </c>
+      <c r="O631" t="s">
+        <v>5056</v>
+      </c>
+      <c r="P631" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q631" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632">
+        <v>633</v>
+      </c>
+      <c r="B632" t="s">
+        <v>5057</v>
+      </c>
+      <c r="C632">
+        <v>220</v>
+      </c>
+      <c r="D632">
+        <v>12</v>
+      </c>
+      <c r="E632" t="s">
+        <v>5058</v>
+      </c>
+      <c r="F632">
+        <v>1</v>
+      </c>
+      <c r="G632">
+        <v>7</v>
+      </c>
+      <c r="H632" t="s">
+        <v>5059</v>
+      </c>
+      <c r="I632" t="s">
+        <v>5060</v>
+      </c>
+      <c r="J632">
+        <v>10</v>
+      </c>
+      <c r="K632">
+        <v>2</v>
+      </c>
+      <c r="L632" t="s">
+        <v>5061</v>
+      </c>
+      <c r="M632" t="s">
+        <v>5062</v>
+      </c>
+      <c r="N632" t="s">
+        <v>5063</v>
+      </c>
+      <c r="O632" t="s">
+        <v>5064</v>
+      </c>
+      <c r="P632" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q632" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633">
+        <v>634</v>
+      </c>
+      <c r="B633" t="s">
+        <v>5065</v>
+      </c>
+      <c r="C633">
+        <v>220</v>
+      </c>
+      <c r="D633">
+        <v>330</v>
+      </c>
+      <c r="E633" t="s">
+        <v>5066</v>
+      </c>
+      <c r="F633">
+        <v>1</v>
+      </c>
+      <c r="G633">
+        <v>7</v>
+      </c>
+      <c r="H633" t="s">
+        <v>5067</v>
+      </c>
+      <c r="I633" t="s">
+        <v>5068</v>
+      </c>
+      <c r="J633">
+        <v>10</v>
+      </c>
+      <c r="K633">
+        <v>2</v>
+      </c>
+      <c r="L633" t="s">
+        <v>5069</v>
+      </c>
+      <c r="M633" t="s">
+        <v>5070</v>
+      </c>
+      <c r="N633" t="s">
+        <v>5071</v>
+      </c>
+      <c r="O633" t="s">
+        <v>5072</v>
+      </c>
+      <c r="P633" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q633" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634">
+        <v>635</v>
+      </c>
+      <c r="B634" t="s">
+        <v>5073</v>
+      </c>
+      <c r="C634">
+        <v>220</v>
+      </c>
+      <c r="D634">
+        <v>331</v>
+      </c>
+      <c r="E634" t="s">
+        <v>5074</v>
+      </c>
+      <c r="F634">
+        <v>1</v>
+      </c>
+      <c r="G634">
+        <v>6</v>
+      </c>
+      <c r="H634" t="s">
+        <v>5075</v>
+      </c>
+      <c r="I634" t="s">
+        <v>5076</v>
+      </c>
+      <c r="J634">
+        <v>10</v>
+      </c>
+      <c r="K634">
+        <v>2</v>
+      </c>
+      <c r="L634" t="s">
+        <v>5077</v>
+      </c>
+      <c r="M634" t="s">
+        <v>5078</v>
+      </c>
+      <c r="N634" t="s">
+        <v>5079</v>
+      </c>
+      <c r="O634" t="s">
+        <v>5080</v>
+      </c>
+      <c r="P634" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q634" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635">
+        <v>636</v>
+      </c>
+      <c r="B635" t="s">
+        <v>5081</v>
+      </c>
+      <c r="C635">
+        <v>220</v>
+      </c>
+      <c r="D635">
+        <v>61</v>
+      </c>
+      <c r="E635" t="s">
+        <v>5082</v>
+      </c>
+      <c r="F635">
+        <v>1</v>
+      </c>
+      <c r="G635">
+        <v>3</v>
+      </c>
+      <c r="H635" t="s">
+        <v>5083</v>
+      </c>
+      <c r="I635" t="s">
+        <v>5084</v>
+      </c>
+      <c r="J635">
+        <v>10</v>
+      </c>
+      <c r="K635">
+        <v>2</v>
+      </c>
+      <c r="L635" t="s">
+        <v>5085</v>
+      </c>
+      <c r="M635" t="s">
+        <v>5086</v>
+      </c>
+      <c r="N635" t="s">
+        <v>5087</v>
+      </c>
+      <c r="O635" t="s">
+        <v>5088</v>
+      </c>
+      <c r="P635" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q635" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636">
+        <v>637</v>
+      </c>
+      <c r="B636" t="s">
+        <v>5089</v>
+      </c>
+      <c r="C636">
+        <v>220</v>
+      </c>
+      <c r="D636">
+        <v>52</v>
+      </c>
+      <c r="E636" t="s">
+        <v>5090</v>
+      </c>
+      <c r="F636">
+        <v>1</v>
+      </c>
+      <c r="G636">
+        <v>2</v>
+      </c>
+      <c r="H636" t="s">
+        <v>5091</v>
+      </c>
+      <c r="I636" t="s">
+        <v>5092</v>
+      </c>
+      <c r="J636">
+        <v>10</v>
+      </c>
+      <c r="K636">
+        <v>2</v>
+      </c>
+      <c r="L636" t="s">
+        <v>5093</v>
+      </c>
+      <c r="M636" t="s">
+        <v>5094</v>
+      </c>
+      <c r="N636" t="s">
+        <v>5095</v>
+      </c>
+      <c r="O636" t="s">
+        <v>5096</v>
+      </c>
+      <c r="P636" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q636" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637">
+        <v>638</v>
+      </c>
+      <c r="B637" t="s">
+        <v>5097</v>
+      </c>
+      <c r="C637">
+        <v>220</v>
+      </c>
+      <c r="D637">
+        <v>90</v>
+      </c>
+      <c r="E637" t="s">
+        <v>5098</v>
+      </c>
+      <c r="F637">
+        <v>1</v>
+      </c>
+      <c r="G637">
+        <v>6</v>
+      </c>
+      <c r="H637" t="s">
+        <v>5099</v>
+      </c>
+      <c r="I637" t="s">
+        <v>5100</v>
+      </c>
+      <c r="J637">
+        <v>10</v>
+      </c>
+      <c r="K637">
+        <v>2</v>
+      </c>
+      <c r="L637" t="s">
+        <v>5101</v>
+      </c>
+      <c r="M637" t="s">
+        <v>5102</v>
+      </c>
+      <c r="N637" t="s">
+        <v>5103</v>
+      </c>
+      <c r="O637" t="s">
+        <v>5104</v>
+      </c>
+      <c r="P637" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q637" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638">
+        <v>639</v>
+      </c>
+      <c r="B638" t="s">
+        <v>5105</v>
+      </c>
+      <c r="C638">
+        <v>220</v>
+      </c>
+      <c r="D638">
+        <v>8</v>
+      </c>
+      <c r="E638" t="s">
+        <v>5106</v>
+      </c>
+      <c r="F638">
+        <v>1</v>
+      </c>
+      <c r="G638">
+        <v>11</v>
+      </c>
+      <c r="H638" t="s">
+        <v>5107</v>
+      </c>
+      <c r="I638" t="s">
+        <v>5108</v>
+      </c>
+      <c r="J638">
+        <v>90</v>
+      </c>
+      <c r="K638">
+        <v>4</v>
+      </c>
+      <c r="L638" t="s">
+        <v>5109</v>
+      </c>
+      <c r="M638" t="s">
+        <v>5110</v>
+      </c>
+      <c r="N638" t="s">
+        <v>5111</v>
+      </c>
+      <c r="O638" t="s">
+        <v>5112</v>
+      </c>
+      <c r="P638" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q638" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639">
+        <v>640</v>
+      </c>
+      <c r="B639" t="s">
+        <v>5113</v>
+      </c>
+      <c r="C639">
+        <v>220</v>
+      </c>
+      <c r="D639">
+        <v>317</v>
+      </c>
+      <c r="E639" t="s">
+        <v>5114</v>
+      </c>
+      <c r="F639">
+        <v>1</v>
+      </c>
+      <c r="G639">
+        <v>7</v>
+      </c>
+      <c r="H639" t="s">
+        <v>5115</v>
+      </c>
+      <c r="I639" t="s">
+        <v>5116</v>
+      </c>
+      <c r="J639">
+        <v>10</v>
+      </c>
+      <c r="K639">
+        <v>2</v>
+      </c>
+      <c r="L639" t="s">
+        <v>5117</v>
+      </c>
+      <c r="M639" t="s">
+        <v>5118</v>
+      </c>
+      <c r="N639" t="s">
+        <v>5119</v>
+      </c>
+      <c r="O639" t="s">
+        <v>5120</v>
+      </c>
+      <c r="P639" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q639" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640">
+        <v>641</v>
+      </c>
+      <c r="B640" t="s">
+        <v>5121</v>
+      </c>
+      <c r="C640">
+        <v>220</v>
+      </c>
+      <c r="D640">
+        <v>278</v>
+      </c>
+      <c r="E640" t="s">
+        <v>5122</v>
+      </c>
+      <c r="F640">
+        <v>1</v>
+      </c>
+      <c r="G640">
+        <v>6</v>
+      </c>
+      <c r="H640" t="s">
+        <v>5123</v>
+      </c>
+      <c r="I640" t="s">
+        <v>5124</v>
+      </c>
+      <c r="J640">
+        <v>10</v>
+      </c>
+      <c r="K640">
+        <v>2</v>
+      </c>
+      <c r="L640" t="s">
+        <v>5125</v>
+      </c>
+      <c r="M640" t="s">
+        <v>5126</v>
+      </c>
+      <c r="N640" t="s">
+        <v>5127</v>
+      </c>
+      <c r="O640" t="s">
+        <v>5128</v>
+      </c>
+      <c r="P640" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q640" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641">
+        <v>642</v>
+      </c>
+      <c r="B641" t="s">
+        <v>5129</v>
+      </c>
+      <c r="C641">
+        <v>220</v>
+      </c>
+      <c r="D641">
+        <v>332</v>
+      </c>
+      <c r="E641" t="s">
+        <v>5130</v>
+      </c>
+      <c r="F641">
+        <v>1</v>
+      </c>
+      <c r="G641">
+        <v>9</v>
+      </c>
+      <c r="H641" t="s">
+        <v>5131</v>
+      </c>
+      <c r="I641" t="s">
+        <v>5132</v>
+      </c>
+      <c r="J641">
+        <v>10</v>
+      </c>
+      <c r="K641">
+        <v>2</v>
+      </c>
+      <c r="L641" t="s">
+        <v>5133</v>
+      </c>
+      <c r="M641" t="s">
+        <v>5134</v>
+      </c>
+      <c r="N641" t="s">
+        <v>5135</v>
+      </c>
+      <c r="O641" t="s">
+        <v>5136</v>
+      </c>
+      <c r="P641" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q641" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642">
+        <v>643</v>
+      </c>
+      <c r="B642" t="s">
+        <v>5137</v>
+      </c>
+      <c r="C642">
+        <v>220</v>
+      </c>
+      <c r="D642">
+        <v>333</v>
+      </c>
+      <c r="E642" t="s">
+        <v>5138</v>
+      </c>
+      <c r="F642">
+        <v>1</v>
+      </c>
+      <c r="G642">
+        <v>2</v>
+      </c>
+      <c r="H642" t="s">
+        <v>5139</v>
+      </c>
+      <c r="I642" t="s">
+        <v>5140</v>
+      </c>
+      <c r="J642">
+        <v>50</v>
+      </c>
+      <c r="K642">
+        <v>4</v>
+      </c>
+      <c r="L642" t="s">
+        <v>5141</v>
+      </c>
+      <c r="M642" t="s">
+        <v>5142</v>
+      </c>
+      <c r="N642" t="s">
+        <v>5143</v>
+      </c>
+      <c r="O642" t="s">
+        <v>5144</v>
+      </c>
+      <c r="P642" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q642" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643">
+        <v>644</v>
+      </c>
+      <c r="B643" t="s">
+        <v>5145</v>
+      </c>
+      <c r="C643">
+        <v>220</v>
+      </c>
+      <c r="D643">
+        <v>332</v>
+      </c>
+      <c r="E643" t="s">
+        <v>5146</v>
+      </c>
+      <c r="F643">
+        <v>1</v>
+      </c>
+      <c r="G643">
+        <v>9</v>
+      </c>
+      <c r="H643" t="s">
+        <v>5147</v>
+      </c>
+      <c r="I643" t="s">
+        <v>5148</v>
+      </c>
+      <c r="J643">
+        <v>10</v>
+      </c>
+      <c r="K643">
+        <v>2</v>
+      </c>
+      <c r="L643" t="s">
+        <v>5149</v>
+      </c>
+      <c r="M643" t="s">
+        <v>5150</v>
+      </c>
+      <c r="N643" t="s">
+        <v>5151</v>
+      </c>
+      <c r="O643" t="s">
+        <v>5152</v>
+      </c>
+      <c r="P643" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q643" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644">
+        <v>645</v>
+      </c>
+      <c r="B644" t="s">
+        <v>5153</v>
+      </c>
+      <c r="C644">
+        <v>220</v>
+      </c>
+      <c r="D644">
+        <v>55</v>
+      </c>
+      <c r="E644" t="s">
+        <v>5154</v>
+      </c>
+      <c r="F644">
+        <v>1</v>
+      </c>
+      <c r="G644">
+        <v>6</v>
+      </c>
+      <c r="H644" t="s">
+        <v>5155</v>
+      </c>
+      <c r="I644" t="s">
+        <v>5156</v>
+      </c>
+      <c r="J644">
+        <v>10</v>
+      </c>
+      <c r="K644">
+        <v>2</v>
+      </c>
+      <c r="L644" t="s">
+        <v>5157</v>
+      </c>
+      <c r="M644" t="s">
+        <v>5158</v>
+      </c>
+      <c r="N644" t="s">
+        <v>5159</v>
+      </c>
+      <c r="O644" t="s">
+        <v>5160</v>
+      </c>
+      <c r="P644" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q644" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645">
+        <v>646</v>
+      </c>
+      <c r="B645" t="s">
+        <v>5161</v>
+      </c>
+      <c r="C645">
+        <v>220</v>
+      </c>
+      <c r="D645">
+        <v>334</v>
+      </c>
+      <c r="E645" t="s">
+        <v>5162</v>
+      </c>
+      <c r="F645">
+        <v>1</v>
+      </c>
+      <c r="G645">
+        <v>7</v>
+      </c>
+      <c r="H645" t="s">
+        <v>5163</v>
+      </c>
+      <c r="I645" t="s">
+        <v>5164</v>
+      </c>
+      <c r="J645">
+        <v>10</v>
+      </c>
+      <c r="K645">
+        <v>2</v>
+      </c>
+      <c r="L645" t="s">
+        <v>5165</v>
+      </c>
+      <c r="M645" t="s">
+        <v>5166</v>
+      </c>
+      <c r="N645" t="s">
+        <v>5167</v>
+      </c>
+      <c r="O645" t="s">
+        <v>5168</v>
+      </c>
+      <c r="P645" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q645" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646">
+        <v>647</v>
+      </c>
+      <c r="B646" t="s">
+        <v>5169</v>
+      </c>
+      <c r="C646">
+        <v>220</v>
+      </c>
+      <c r="D646">
+        <v>12</v>
+      </c>
+      <c r="E646" t="s">
+        <v>5170</v>
+      </c>
+      <c r="F646">
+        <v>1</v>
+      </c>
+      <c r="G646">
+        <v>7</v>
+      </c>
+      <c r="H646" t="s">
+        <v>5171</v>
+      </c>
+      <c r="I646" t="s">
+        <v>5172</v>
+      </c>
+      <c r="J646">
+        <v>10</v>
+      </c>
+      <c r="K646">
+        <v>2</v>
+      </c>
+      <c r="L646" t="s">
+        <v>5173</v>
+      </c>
+      <c r="M646" t="s">
+        <v>5174</v>
+      </c>
+      <c r="N646" t="s">
+        <v>5175</v>
+      </c>
+      <c r="O646" t="s">
+        <v>5176</v>
+      </c>
+      <c r="P646" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q646" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647">
+        <v>648</v>
+      </c>
+      <c r="B647" t="s">
+        <v>5177</v>
+      </c>
+      <c r="C647">
+        <v>220</v>
+      </c>
+      <c r="D647">
+        <v>334</v>
+      </c>
+      <c r="E647" t="s">
+        <v>5178</v>
+      </c>
+      <c r="F647">
+        <v>1</v>
+      </c>
+      <c r="G647">
+        <v>7</v>
+      </c>
+      <c r="H647" t="s">
+        <v>5179</v>
+      </c>
+      <c r="I647" t="s">
+        <v>5180</v>
+      </c>
+      <c r="J647">
+        <v>10</v>
+      </c>
+      <c r="K647">
+        <v>2</v>
+      </c>
+      <c r="L647" t="s">
+        <v>5181</v>
+      </c>
+      <c r="M647" t="s">
+        <v>5182</v>
+      </c>
+      <c r="N647" t="s">
+        <v>5183</v>
+      </c>
+      <c r="O647" t="s">
+        <v>5184</v>
+      </c>
+      <c r="P647" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q647" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648">
+        <v>649</v>
+      </c>
+      <c r="B648" t="s">
+        <v>5185</v>
+      </c>
+      <c r="C648">
+        <v>220</v>
+      </c>
+      <c r="D648">
+        <v>8</v>
+      </c>
+      <c r="E648" t="s">
+        <v>5186</v>
+      </c>
+      <c r="F648">
+        <v>1</v>
+      </c>
+      <c r="G648">
+        <v>11</v>
+      </c>
+      <c r="H648" t="s">
+        <v>5187</v>
+      </c>
+      <c r="I648" t="s">
+        <v>5188</v>
+      </c>
+      <c r="J648">
+        <v>90</v>
+      </c>
+      <c r="K648">
+        <v>4</v>
+      </c>
+      <c r="L648" t="s">
+        <v>5189</v>
+      </c>
+      <c r="M648" t="s">
+        <v>5190</v>
+      </c>
+      <c r="N648" t="s">
+        <v>5191</v>
+      </c>
+      <c r="O648" t="s">
+        <v>5192</v>
+      </c>
+      <c r="P648" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q648" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649">
+        <v>650</v>
+      </c>
+      <c r="B649" t="s">
+        <v>5193</v>
+      </c>
+      <c r="C649">
+        <v>220</v>
+      </c>
+      <c r="D649">
+        <v>63</v>
+      </c>
+      <c r="E649" t="s">
+        <v>5194</v>
+      </c>
+      <c r="F649">
+        <v>1</v>
+      </c>
+      <c r="G649">
+        <v>3</v>
+      </c>
+      <c r="H649" t="s">
+        <v>5195</v>
+      </c>
+      <c r="I649" t="s">
+        <v>5196</v>
+      </c>
+      <c r="J649">
+        <v>10</v>
+      </c>
+      <c r="K649">
+        <v>2</v>
+      </c>
+      <c r="L649" t="s">
+        <v>5197</v>
+      </c>
+      <c r="M649" t="s">
+        <v>5198</v>
+      </c>
+      <c r="N649" t="s">
+        <v>5199</v>
+      </c>
+      <c r="O649" t="s">
+        <v>5200</v>
+      </c>
+      <c r="P649" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q649" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650">
+        <v>651</v>
+      </c>
+      <c r="B650" t="s">
+        <v>5201</v>
+      </c>
+      <c r="C650">
+        <v>220</v>
+      </c>
+      <c r="D650">
+        <v>62</v>
+      </c>
+      <c r="E650" t="s">
+        <v>5202</v>
+      </c>
+      <c r="F650">
+        <v>1</v>
+      </c>
+      <c r="G650">
+        <v>3</v>
+      </c>
+      <c r="H650" t="s">
+        <v>5203</v>
+      </c>
+      <c r="I650" t="s">
+        <v>5204</v>
+      </c>
+      <c r="J650">
+        <v>10</v>
+      </c>
+      <c r="K650">
+        <v>2</v>
+      </c>
+      <c r="L650" t="s">
+        <v>5205</v>
+      </c>
+      <c r="M650" t="s">
+        <v>5206</v>
+      </c>
+      <c r="N650" t="s">
+        <v>5207</v>
+      </c>
+      <c r="O650" t="s">
+        <v>5208</v>
+      </c>
+      <c r="P650" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q650" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651">
+        <v>652</v>
+      </c>
+      <c r="B651" t="s">
+        <v>5209</v>
+      </c>
+      <c r="C651">
+        <v>220</v>
+      </c>
+      <c r="D651">
+        <v>9</v>
+      </c>
+      <c r="E651" t="s">
+        <v>5210</v>
+      </c>
+      <c r="F651">
+        <v>1</v>
+      </c>
+      <c r="G651">
+        <v>11</v>
+      </c>
+      <c r="H651" t="s">
+        <v>5211</v>
+      </c>
+      <c r="I651" t="s">
+        <v>5212</v>
+      </c>
+      <c r="J651">
+        <v>90</v>
+      </c>
+      <c r="K651">
+        <v>4</v>
+      </c>
+      <c r="L651" t="s">
+        <v>5213</v>
+      </c>
+      <c r="M651" t="s">
+        <v>5214</v>
+      </c>
+      <c r="N651" t="s">
+        <v>5215</v>
+      </c>
+      <c r="O651" t="s">
+        <v>5216</v>
+      </c>
+      <c r="P651" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q651" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652">
+        <v>653</v>
+      </c>
+      <c r="B652" t="s">
+        <v>5217</v>
+      </c>
+      <c r="C652">
+        <v>220</v>
+      </c>
+      <c r="D652">
+        <v>24</v>
+      </c>
+      <c r="E652" t="s">
+        <v>5218</v>
+      </c>
+      <c r="F652">
+        <v>1</v>
+      </c>
+      <c r="G652">
+        <v>7</v>
+      </c>
+      <c r="H652" t="s">
+        <v>5219</v>
+      </c>
+      <c r="I652" t="s">
+        <v>5220</v>
+      </c>
+      <c r="J652">
+        <v>10</v>
+      </c>
+      <c r="K652">
+        <v>2</v>
+      </c>
+      <c r="L652" t="s">
+        <v>5221</v>
+      </c>
+      <c r="M652" t="s">
+        <v>5222</v>
+      </c>
+      <c r="N652" t="s">
+        <v>5223</v>
+      </c>
+      <c r="O652" t="s">
+        <v>5224</v>
+      </c>
+      <c r="P652" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="Q652" s="2">
+        <v>46108.5</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>